--- a/public/build/assets/files/objective.xlsx
+++ b/public/build/assets/files/objective.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Lms\lms\public\build\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B02BD27-CAAF-4CEE-B3D9-0EB0AE692E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20700" windowHeight="7005"/>
+    <workbookView xWindow="7020" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quiz" sheetId="1" r:id="rId1"/>
@@ -27,9 +28,6 @@
     <t>C</t>
   </si>
   <si>
-    <t>Marks</t>
-  </si>
-  <si>
     <t>midrib</t>
   </si>
   <si>
@@ -127,12 +125,15 @@
   </si>
   <si>
     <t>answer</t>
+  </si>
+  <si>
+    <t>marks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -534,7 +535,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -546,42 +547,42 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>6</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>1</v>
@@ -592,19 +593,19 @@
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>11</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>1</v>
@@ -615,19 +616,19 @@
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>1</v>
@@ -638,19 +639,19 @@
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>16</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>0</v>
@@ -661,19 +662,19 @@
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>1</v>
@@ -684,19 +685,19 @@
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>1</v>
